--- a/Wumple/Grading/2 stage/6-examples/Wumple_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/Wumple/Grading/2 stage/6-examples/Wumple_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wumple" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gemini Generation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Wumple" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gemini 3.1 Pro Generation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C1" s="24" t="inlineStr">
         <is>
-          <t>GPT-5 Generation</t>
+          <t>Grading</t>
         </is>
       </c>
       <c r="D1" s="25" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="D2" s="27" t="inlineStr">
         <is>
-          <t>Represented as [*] --&gt; Watch</t>
+          <t>Correctly represented by the initial transition to Watch.</t>
         </is>
       </c>
       <c r="E2" s="6" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="D3" s="28" t="inlineStr">
         <is>
-          <t>No initialization action on the initial transition to Watch</t>
+          <t>No initialization actions are present on the initial transition.</t>
         </is>
       </c>
       <c r="E3" s="6" t="n"/>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="D4" s="27" t="inlineStr">
         <is>
-          <t>Watch is correctly modeled as a composite state with multiple regions</t>
+          <t>Correctly represented by the Watch state.</t>
         </is>
       </c>
       <c r="E4" s="6" t="n"/>
@@ -6902,11 +6902,11 @@
         </is>
       </c>
       <c r="C5" s="27" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D5" s="27" t="inlineStr">
         <is>
-          <t>Represented as region Backlight which captures similar functionality but differs in structure (missing Flash state)</t>
+          <t>Correctly represented by the Backlight region.</t>
         </is>
       </c>
       <c r="E5" s="6" t="n"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>Represented as [*] --&gt; BacklightOff in Backlight region</t>
+          <t>Correctly represented by the initial transition to BacklightOff.</t>
         </is>
       </c>
       <c r="E6" s="6" t="n"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>Represented as BacklightOff state</t>
+          <t>Correctly represented by BacklightOff.</t>
         </is>
       </c>
       <c r="E7" s="6" t="n"/>
@@ -6968,11 +6968,11 @@
         </is>
       </c>
       <c r="C8" s="27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>Represented as entry / turnBacklightOff() which is semantically equivalent</t>
+          <t>No entry action defined for BacklightOff.</t>
         </is>
       </c>
       <c r="E8" s="6" t="n"/>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
-          <t>Represented as BacklightOff --&gt; BacklightOn : D</t>
+          <t>Correctly represented by BacklightOff --&gt; BacklightOn : D.</t>
         </is>
       </c>
       <c r="E9" s="6" t="n"/>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
-          <t>Represented as BacklightOn state</t>
+          <t>Correctly represented by BacklightOn.</t>
         </is>
       </c>
       <c r="E10" s="6" t="n"/>
@@ -7034,11 +7034,11 @@
         </is>
       </c>
       <c r="C11" s="27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>Represented as entry / turnBacklightOn() which is semantically equivalent</t>
+          <t>No entry action defined for BacklightOn.</t>
         </is>
       </c>
       <c r="E11" s="6" t="n"/>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Represented as BacklightOn --&gt; BacklightOff : D</t>
+          <t>Correctly represented by BacklightOn --&gt; BacklightOff : D.</t>
         </is>
       </c>
       <c r="E12" s="6" t="n"/>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>Represented as BacklightOn --&gt; BacklightOff : after10sec</t>
+          <t>Correctly represented by BacklightOn --&gt; BacklightOff : after_10s.</t>
         </is>
       </c>
       <c r="E13" s="6" t="n"/>
@@ -7100,11 +7100,11 @@
         </is>
       </c>
       <c r="C14" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>No Flash state or transition to Flash state in Backlight region</t>
+          <t>Correctly represented by transitions to BacklightFlashing on alarmTimeReached and countdownReachedZero.</t>
         </is>
       </c>
       <c r="E14" s="6" t="n"/>
@@ -7122,11 +7122,11 @@
         </is>
       </c>
       <c r="C15" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>No guard condition for flash transition (Flash state not present)</t>
+          <t>Correctly represented by [flashAlertOn].</t>
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
@@ -7144,11 +7144,11 @@
         </is>
       </c>
       <c r="C16" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>No Flash state in the Backlight region</t>
+          <t>Correctly represented by BacklightFlashing.</t>
         </is>
       </c>
       <c r="E16" s="6" t="n"/>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>No flash5Sec() action (Flash state not present)</t>
+          <t>No do action defined for BacklightFlashing.</t>
         </is>
       </c>
       <c r="E17" s="6" t="n"/>
@@ -7206,11 +7206,11 @@
         </is>
       </c>
       <c r="C18" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="27" t="inlineStr">
         <is>
-          <t>No transition from Flash to Off (Flash state not present)</t>
+          <t>Correctly represented by the transition from BacklightOff to BacklightFlashing (assuming typo in rubric for Off =&gt; Flash).</t>
         </is>
       </c>
       <c r="E18" s="6" t="n"/>
@@ -7228,11 +7228,11 @@
         </is>
       </c>
       <c r="C19" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="27" t="inlineStr">
         <is>
-          <t>No guard condition for flash transition (Flash state not present)</t>
+          <t>Correctly represented by [flashAlertOn] on the transition from BacklightOff.</t>
         </is>
       </c>
       <c r="E19" s="6" t="n"/>
@@ -7250,11 +7250,11 @@
         </is>
       </c>
       <c r="C20" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
-          <t>No anyButton transition from Flash (Flash state not present)</t>
+          <t>Correctly represented by BacklightFlashing --&gt; BacklightOff : anyButton.</t>
         </is>
       </c>
       <c r="E20" s="6" t="n"/>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="D21" s="27" t="inlineStr">
         <is>
-          <t>Represented as region UserInterface which contains the watch mode logic</t>
+          <t>Correctly represented by the Main region.</t>
         </is>
       </c>
       <c r="E21" s="6" t="n"/>
@@ -7294,11 +7294,11 @@
         </is>
       </c>
       <c r="C22" s="30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
-          <t>Initial state goes to NormalOperation which contains modes but no explicit AlarmOff composite state</t>
+          <t>Correctly represented by the initial transition to NormalOperation.</t>
         </is>
       </c>
       <c r="E22" s="6" t="n"/>
@@ -7316,11 +7316,11 @@
         </is>
       </c>
       <c r="C23" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="27" t="inlineStr">
         <is>
-          <t>No AlarmOff composite state; alarm on/off is modeled in separate AlarmSwitch region</t>
+          <t>Correctly represented by NormalOperation.</t>
         </is>
       </c>
       <c r="E23" s="6" t="n"/>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="D24" s="27" t="inlineStr">
         <is>
-          <t>NormalOperation starts with [*] --&gt; TimekeepingMode</t>
+          <t>Correctly represented by the initial transition to Timekeeping.</t>
         </is>
       </c>
       <c r="E24" s="6" t="n"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimekeepingMode composite state</t>
+          <t>Correctly represented by Timekeeping.</t>
         </is>
       </c>
       <c r="E25" s="6" t="n"/>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="D26" s="27" t="inlineStr">
         <is>
-          <t>TimekeepingMode starts with [*] --&gt; TimeDisplay</t>
+          <t>Correctly represented by the initial transition to ShowTime.</t>
         </is>
       </c>
       <c r="E26" s="6" t="n"/>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D27" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimeDisplay state</t>
+          <t>Correctly represented by ShowTime.</t>
         </is>
       </c>
       <c r="E27" s="6" t="n"/>
@@ -7444,11 +7444,11 @@
         </is>
       </c>
       <c r="C28" s="27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: showCurrentTime() which is semantically equivalent</t>
+          <t>No do action defined for ShowTime.</t>
         </is>
       </c>
       <c r="E28" s="6" t="n"/>
@@ -7466,11 +7466,11 @@
         </is>
       </c>
       <c r="C29" s="27" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D29" s="27" t="inlineStr">
         <is>
-          <t>B held for 2 seconds is in FlashAlertSwitch region as Bheld2sec but not as self-transition on TimeDisplay</t>
+          <t>Correctly represented by ShowTime --&gt; ShowTime : B_held_2s.</t>
         </is>
       </c>
       <c r="E29" s="6" t="n"/>
@@ -7488,11 +7488,11 @@
         </is>
       </c>
       <c r="C30" s="27" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D30" s="27" t="inlineStr">
         <is>
-          <t>B press for alarm toggle is in AlarmSwitch region but not as self-transition on TimeDisplay</t>
+          <t>Correctly represented by toggleFlashAlert().</t>
         </is>
       </c>
       <c r="E30" s="6" t="n"/>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="D31" s="27" t="inlineStr">
         <is>
-          <t>Represented as enableFlashAlert() / disableFlashAlert() in FlashAlertSwitch region</t>
+          <t>Correctly represented by ShowTime --&gt; ShowTime : B.</t>
         </is>
       </c>
       <c r="E31" s="6" t="n"/>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="D32" s="27" t="inlineStr">
         <is>
-          <t>Represented as enableAlarm() / disableAlarm() in AlarmSwitch region</t>
+          <t>Correctly represented by toggleAlarm().</t>
         </is>
       </c>
       <c r="E32" s="6" t="n"/>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="D33" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimeDisplay --&gt; TimeSetSeconds : C</t>
+          <t>Correctly represented by ShowTime --&gt; SetTime : C and initial transition to SetSeconds.</t>
         </is>
       </c>
       <c r="E33" s="6" t="n"/>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="D34" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashCurrentSeconds() in TimeSetSeconds state</t>
+          <t>Correctly represented by the note with do: flash() for SetSeconds.</t>
         </is>
       </c>
       <c r="E34" s="6" t="n"/>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="D35" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimeDisplay --&gt; AlarmMode : A</t>
+          <t>Correctly represented by ShowTime --&gt; Alarm : A.</t>
         </is>
       </c>
       <c r="E35" s="6" t="n"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D36" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimeSetSeconds state</t>
+          <t>Correctly represented by SetSeconds.</t>
         </is>
       </c>
       <c r="E36" s="6" t="n"/>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="D37" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimeSetSeconds --&gt; TimeSetSeconds : B / incrementCurrentSeconds()</t>
+          <t>Correctly represented by SetSeconds --&gt; SetSeconds : B.</t>
         </is>
       </c>
       <c r="E37" s="6" t="n"/>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="D38" s="27" t="inlineStr">
         <is>
-          <t>Represented as incrementCurrentSeconds() which is semantically equivalent</t>
+          <t>Correctly represented by incrementSeconds().</t>
         </is>
       </c>
       <c r="E38" s="6" t="n"/>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D39" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimeSetSeconds --&gt; TimeSetMinutes : C</t>
+          <t>Correctly represented by SetSeconds --&gt; SetMinutes : C.</t>
         </is>
       </c>
       <c r="E39" s="6" t="n"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="D40" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashCurrentMinutes() in TimeSetMinutes state</t>
+          <t>Correctly represented by the note with do: flash() for SetMinutes.</t>
         </is>
       </c>
       <c r="E40" s="6" t="n"/>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="D41" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimeSetMinutes state</t>
+          <t>Correctly represented by SetMinutes.</t>
         </is>
       </c>
       <c r="E41" s="6" t="n"/>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="D42" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimeSetMinutes --&gt; TimeSetMinutes : B / incrementCurrentMinutes()</t>
+          <t>Correctly represented by SetMinutes --&gt; SetMinutes : B.</t>
         </is>
       </c>
       <c r="E42" s="6" t="n"/>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="D43" s="27" t="inlineStr">
         <is>
-          <t>Represented as incrementCurrentMinutes() which is semantically equivalent</t>
+          <t>Correctly represented by incrementMinutes().</t>
         </is>
       </c>
       <c r="E43" s="6" t="n"/>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="D44" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimeSetMinutes --&gt; TimeSetHours : C</t>
+          <t>Correctly represented by SetMinutes --&gt; SetHours : C.</t>
         </is>
       </c>
       <c r="E44" s="6" t="n"/>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="D45" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashCurrentHours() in TimeSetHours state</t>
+          <t>Correctly represented by the note with do: flash() for SetHours.</t>
         </is>
       </c>
       <c r="E45" s="6" t="n"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="D46" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimeSetHours state</t>
+          <t>Correctly represented by SetHours.</t>
         </is>
       </c>
       <c r="E46" s="6" t="n"/>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="D47" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimeSetHours --&gt; TimeSetHours : B / incrementCurrentHours()</t>
+          <t>Correctly represented by SetHours --&gt; SetHours : B.</t>
         </is>
       </c>
       <c r="E47" s="6" t="n"/>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="D48" s="27" t="inlineStr">
         <is>
-          <t>Represented as incrementCurrentHours() which is semantically equivalent</t>
+          <t>Correctly represented by incrementHours().</t>
         </is>
       </c>
       <c r="E48" s="6" t="n"/>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="D49" s="27" t="inlineStr">
         <is>
-          <t>Represented as TimeSetHours --&gt; TimeSetSeconds : C</t>
+          <t>Correctly represented by SetHours --&gt; SetSeconds : C.</t>
         </is>
       </c>
       <c r="E49" s="6" t="n"/>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="D50" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashCurrentSeconds() in TimeSetSeconds state</t>
+          <t>Correctly represented by the note with do: flash() for SetSeconds.</t>
         </is>
       </c>
       <c r="E50" s="6" t="n"/>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="D51" s="27" t="inlineStr">
         <is>
-          <t>Represented as transitions from TimeSet states to TimeDisplay : A then TimeDisplay --&gt; AlarmMode : A</t>
+          <t>Correctly represented by ShowTime --&gt; Alarm : A.</t>
         </is>
       </c>
       <c r="E51" s="6" t="n"/>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="D52" s="27" t="inlineStr">
         <is>
-          <t>Represented as AlarmMode composite state</t>
+          <t>Correctly represented by Alarm.</t>
         </is>
       </c>
       <c r="E52" s="6" t="n"/>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="D53" s="27" t="inlineStr">
         <is>
-          <t>AlarmMode starts with [*] --&gt; AlarmDisplay</t>
+          <t>Correctly represented by the initial transition to ShowAlarm.</t>
         </is>
       </c>
       <c r="E53" s="6" t="n"/>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="D54" s="27" t="inlineStr">
         <is>
-          <t>Represented as AlarmDisplay state</t>
+          <t>Correctly represented by ShowAlarm.</t>
         </is>
       </c>
       <c r="E54" s="6" t="n"/>
@@ -8254,11 +8254,11 @@
         </is>
       </c>
       <c r="C55" s="27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: showAlarmTime() which is semantically equivalent</t>
+          <t>No entry action defined for ShowAlarm.</t>
         </is>
       </c>
       <c r="E55" s="6" t="n"/>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="D56" s="27" t="inlineStr">
         <is>
-          <t>Represented as AlarmDisplay --&gt; AlarmSetMinutes : C</t>
+          <t>Correctly represented by ShowAlarm --&gt; SetAlarm : C and initial transition to SetAlarmMinutes.</t>
         </is>
       </c>
       <c r="E56" s="6" t="n"/>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="D57" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashAlarmMinutes() in AlarmSetMinutes state</t>
+          <t>Correctly represented by the note with do: flash() for SetAlarmMinutes.</t>
         </is>
       </c>
       <c r="E57" s="6" t="n"/>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="D58" s="27" t="inlineStr">
         <is>
-          <t>Represented as AlarmDisplay --&gt; CountdownMode : A</t>
+          <t>Correctly represented by ShowAlarm --&gt; Countdown : A.</t>
         </is>
       </c>
       <c r="E58" s="6" t="n"/>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="D59" s="27" t="inlineStr">
         <is>
-          <t>Represented as AlarmSetMinutes state</t>
+          <t>Correctly represented by SetAlarmMinutes.</t>
         </is>
       </c>
       <c r="E59" s="6" t="n"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="D60" s="27" t="inlineStr">
         <is>
-          <t>Represented as AlarmSetMinutes --&gt; AlarmSetMinutes : B / incrementAlarmMinutes()</t>
+          <t>Correctly represented by SetAlarmMinutes --&gt; SetAlarmMinutes : B.</t>
         </is>
       </c>
       <c r="E60" s="6" t="n"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="D61" s="27" t="inlineStr">
         <is>
-          <t>Represented as incrementAlarmMinutes() which is semantically equivalent</t>
+          <t>Correctly represented by incrementMinutes().</t>
         </is>
       </c>
       <c r="E61" s="6" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="D62" s="27" t="inlineStr">
         <is>
-          <t>Represented as AlarmSetMinutes --&gt; AlarmSetHours : C</t>
+          <t>Correctly represented by SetAlarmMinutes --&gt; SetAlarmHours : C.</t>
         </is>
       </c>
       <c r="E62" s="6" t="n"/>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="D63" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashAlarmHours() in AlarmSetHours state</t>
+          <t>Correctly represented by the note with do: flash() for SetAlarmHours.</t>
         </is>
       </c>
       <c r="E63" s="6" t="n"/>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="D64" s="27" t="inlineStr">
         <is>
-          <t>Represented as AlarmSetHours state</t>
+          <t>Correctly represented by SetAlarmHours.</t>
         </is>
       </c>
       <c r="E64" s="6" t="n"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="D65" s="27" t="inlineStr">
         <is>
-          <t>Represented as AlarmSetHours --&gt; AlarmSetHours : B / incrementAlarmHours()</t>
+          <t>Correctly represented by SetAlarmHours --&gt; SetAlarmHours : B.</t>
         </is>
       </c>
       <c r="E65" s="6" t="n"/>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="D66" s="27" t="inlineStr">
         <is>
-          <t>Represented as incrementAlarmHours() which is semantically equivalent</t>
+          <t>Correctly represented by incrementHours().</t>
         </is>
       </c>
       <c r="E66" s="6" t="n"/>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="D67" s="27" t="inlineStr">
         <is>
-          <t>Represented as AlarmSetHours --&gt; AlarmSetMinutes : C</t>
+          <t>Correctly represented by SetAlarmHours --&gt; SetAlarmMinutes : C.</t>
         </is>
       </c>
       <c r="E67" s="6" t="n"/>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="D68" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashAlarmMinutes() in AlarmSetMinutes state</t>
+          <t>Correctly represented by the note with do: flash() for SetAlarmMinutes.</t>
         </is>
       </c>
       <c r="E68" s="6" t="n"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="D69" s="27" t="inlineStr">
         <is>
-          <t>Represented as transitions from AlarmSet states to TimekeepingMode : A then AlarmDisplay --&gt; CountdownMode : A</t>
+          <t>Correctly represented by ShowAlarm --&gt; Countdown : A.</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="D70" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownMode composite state</t>
+          <t>Correctly represented by Countdown.</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="D71" s="27" t="inlineStr">
         <is>
-          <t>CountdownMode starts with [*] --&gt; CountdownDisplay</t>
+          <t>Correctly represented by the initial transition to ShowCountdown.</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="D72" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownDisplay state</t>
+          <t>Correctly represented by ShowCountdown.</t>
         </is>
       </c>
     </row>
@@ -8642,11 +8642,11 @@
         </is>
       </c>
       <c r="C73" s="27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: showCountdownTime() which is semantically equivalent</t>
+          <t>No entry action defined for ShowCountdown.</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="D74" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownDisplay --&gt; CountdownSetSeconds : C</t>
+          <t>Correctly represented by ShowCountdown --&gt; SetCountdown : C and initial transition to SetCDSeconds.</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="D75" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashCountdownSeconds() in CountdownSetSeconds state</t>
+          <t>Correctly represented by the note with do: flash() for SetCDSeconds.</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="D76" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownDisplay --&gt; CountdownRunning : B [countdownTimeSet()] / startCountdown()</t>
+          <t>Correctly represented by ShowCountdown --&gt; CountdownRunning : B.</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="D77" s="27" t="inlineStr">
         <is>
-          <t>Represented as [countdownTimeSet()] which is semantically equivalent</t>
+          <t>Correctly represented by [countdownTimeSet].</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="D78" s="27" t="inlineStr">
         <is>
-          <t>Represented as startCountdown() which implies setting target time</t>
+          <t>Correctly represented by startCountdown().</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="D79" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownDisplay --&gt; TimekeepingMode : A</t>
+          <t>Correctly represented by ShowCountdown --&gt; Timekeeping : A and CountdownRunning --&gt; Timekeeping : A.</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D80" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownSetSeconds state</t>
+          <t>Correctly represented by SetCDSeconds.</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="D81" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownSetSeconds --&gt; CountdownSetSeconds : B / incrementCountdownSeconds()</t>
+          <t>Correctly represented by SetCDSeconds --&gt; SetCDSeconds : B.</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="D82" s="27" t="inlineStr">
         <is>
-          <t>Represented as incrementCountdownSeconds() which is semantically equivalent</t>
+          <t>Correctly represented by incrementSeconds().</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="D83" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownSetSeconds --&gt; CountdownSetMinutes : C</t>
+          <t>Correctly represented by SetCDSeconds --&gt; SetCDMinutes : C.</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="D84" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashCountdownMinutes() in CountdownSetMinutes state</t>
+          <t>Correctly represented by the note with do: flash() for SetCDMinutes.</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D85" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownSetMinutes state</t>
+          <t>Correctly represented by SetCDMinutes.</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="D86" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownSetMinutes --&gt; CountdownSetMinutes : B / incrementCountdownMinutes()</t>
+          <t>Correctly represented by SetCDMinutes --&gt; SetCDMinutes : B.</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="D87" s="27" t="inlineStr">
         <is>
-          <t>Represented as incrementCountdownMinutes() which is semantically equivalent</t>
+          <t>Correctly represented by incrementMinutes().</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="D88" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownSetMinutes --&gt; CountdownSetHours : C</t>
+          <t>Correctly represented by SetCDMinutes --&gt; SetCDHours : C.</t>
         </is>
       </c>
     </row>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="D89" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashCountdownHours() in CountdownSetHours state</t>
+          <t>Correctly represented by the note with do: flash() for SetCDHours.</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="D90" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownSetHours state</t>
+          <t>Correctly represented by SetCDHours.</t>
         </is>
       </c>
     </row>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="D91" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownSetHours --&gt; CountdownSetHours : B / incrementCountdownHours()</t>
+          <t>Correctly represented by SetCDHours --&gt; SetCDHours : B.</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D92" s="27" t="inlineStr">
         <is>
-          <t>Represented as incrementCountdownHours() which is semantically equivalent</t>
+          <t>Correctly represented by incrementHours().</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="D93" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownSetHours --&gt; CountdownSetSeconds : C</t>
+          <t>Correctly represented by SetCDHours --&gt; SetCDSeconds : C.</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D94" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashCountdownSeconds() in CountdownSetSeconds state</t>
+          <t>Correctly represented by the note with do: flash() for SetCDSeconds.</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="D95" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownRunning state</t>
+          <t>Correctly represented by CountdownRunning.</t>
         </is>
       </c>
     </row>
@@ -9102,11 +9102,11 @@
         </is>
       </c>
       <c r="C96" s="27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: showCountdownTime() in CountdownRunning state</t>
+          <t>No do action defined for CountdownRunning.</t>
         </is>
       </c>
     </row>
@@ -9122,11 +9122,11 @@
         </is>
       </c>
       <c r="C97" s="27" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D97" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownRunning --&gt; CountdownNotification : after1sec [countdownRemaining() &lt;= 1] / setCountdownZero()</t>
+          <t>Partially represented by NormalOperation --&gt; CountdownRinging : countdownReachedZero (transitions from composite state instead of CountdownRunning).</t>
         </is>
       </c>
     </row>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="D98" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashCountdownZero() in CountdownNotification state</t>
+          <t>Correctly represented by beepAndFlashZeros().</t>
         </is>
       </c>
     </row>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="D99" s="27" t="inlineStr">
         <is>
-          <t>Represented as CountdownNotification state</t>
+          <t>Correctly represented by CountdownRinging.</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="D100" s="27" t="inlineStr">
         <is>
-          <t>Represented as entry / startCountdownBeep() and do: flashCountdownZero() which captures the behavior</t>
+          <t>Correctly represented by beepAndFlashZeros().</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="D101" s="27" t="inlineStr">
         <is>
-          <t>Represented as multiple button transitions from CountdownNotification to CountdownDisplay</t>
+          <t>Correctly represented by CountdownRinging --&gt; Countdown : anyButton.</t>
         </is>
       </c>
     </row>
@@ -9226,7 +9226,7 @@
       </c>
       <c r="D102" s="27" t="inlineStr">
         <is>
-          <t>Represented as state H in NormalOperation</t>
+          <t>Correctly represented by state H.</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="D103" s="27" t="inlineStr">
         <is>
-          <t>Represented as NormalOperation --&gt; AlarmNotification : alarmDue [alarmEnabled()]</t>
+          <t>Correctly represented by NormalOperation --&gt; AlarmRinging : alarmTimeReached.</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="D104" s="27" t="inlineStr">
         <is>
-          <t>No explicit saveDisplay() action; history state H is used instead</t>
+          <t>No saveDisplay action defined.</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="D105" s="27" t="inlineStr">
         <is>
-          <t>Represented as do: flashAlarmTime() in AlarmNotification state</t>
+          <t>Correctly represented by beepAndFlashAlarmTime().</t>
         </is>
       </c>
     </row>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="D106" s="27" t="inlineStr">
         <is>
-          <t>Represented as AlarmNotification state</t>
+          <t>Correctly represented by AlarmRinging.</t>
         </is>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="D107" s="27" t="inlineStr">
         <is>
-          <t>Represented as entry / startAlarmBeep() and do: flashAlarmTime() which captures the behavior</t>
+          <t>Correctly represented by beepAndFlashAlarmTime().</t>
         </is>
       </c>
     </row>
@@ -9346,7 +9346,7 @@
       </c>
       <c r="D108" s="27" t="inlineStr">
         <is>
-          <t>No explicit restoreDisplay() action; transitions to H handle return</t>
+          <t>No restoreDisplay action defined.</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="D109" s="27" t="inlineStr">
         <is>
-          <t>Represented as multiple button transitions from AlarmNotification to H</t>
+          <t>Correctly represented by AlarmRinging --&gt; H : anyButton.</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D110" s="33" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect states present</t>
+          <t>No fundamentally incorrect additional states.</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="D111" s="27" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect transitions present</t>
+          <t>No fundamentally incorrect additional transitions.</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="D112" s="27" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect guards present</t>
+          <t>No fundamentally incorrect additional guards.</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="D113" s="27" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect actions present</t>
+          <t>No fundamentally incorrect additional actions.</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D114" s="27" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect composite states present</t>
+          <t>No fundamentally incorrect additional composite states.</t>
         </is>
       </c>
     </row>
@@ -9482,11 +9482,11 @@
         </is>
       </c>
       <c r="C115" s="27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D115" s="27" t="inlineStr">
         <is>
-          <t>AlarmSwitch and FlashAlertSwitch regions are unnecessary separate regions; Clock region is also unnecessary</t>
+          <t>No fundamentally incorrect additional regions.</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="D116" s="27" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect history states present</t>
+          <t>No fundamentally incorrect additional history states.</t>
         </is>
       </c>
     </row>
@@ -15109,7 +15109,7 @@
     <row r="1" ht="15.75" customHeight="1" s="100">
       <c r="A1" s="101" t="inlineStr">
         <is>
-          <t>Generated by GPT-5</t>
+          <t>Generated by Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="J1" s="43" t="inlineStr">
@@ -15176,15 +15176,15 @@
         <v/>
       </c>
       <c r="C3" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$109, $A3, 'GPT-5 Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D3" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$110:$A$116, $A3, 'GPT-5 Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A3, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E3" s="47">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$109, $A3, 'GPT-5 Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F3" s="47">
@@ -15212,15 +15212,15 @@
         <v/>
       </c>
       <c r="C4" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$109, $A4, 'GPT-5 Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D4" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$110:$A$116, $A4, 'GPT-5 Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A4, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E4" s="47">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$109, $A4, 'GPT-5 Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F4" s="47">
@@ -15252,15 +15252,15 @@
         <v/>
       </c>
       <c r="C5" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$109, $A5, 'GPT-5 Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D5" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$110:$A$116, $A5, 'GPT-5 Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A5, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E5" s="47">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$109, $A5, 'GPT-5 Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F5" s="47">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="J5" s="45" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -15292,15 +15292,15 @@
         <v/>
       </c>
       <c r="C6" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$109, $A6, 'GPT-5 Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D6" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$110:$A$116, $A6, 'GPT-5 Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A6, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E6" s="47">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$109, $A6, 'GPT-5 Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F6" s="47">
@@ -15327,15 +15327,15 @@
         <v/>
       </c>
       <c r="C7" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$109, $A7, 'GPT-5 Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D7" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$110:$A$116, $A7, 'GPT-5 Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A7, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E7" s="47">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$109, $A7, 'GPT-5 Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F7" s="47">
@@ -15367,15 +15367,15 @@
         <v/>
       </c>
       <c r="C8" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$109, $A8, 'GPT-5 Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D8" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$110:$A$116, $A8, 'GPT-5 Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A8, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E8" s="47">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$109, $A8, 'GPT-5 Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F8" s="47">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="J8" s="106" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -15407,15 +15407,15 @@
         <v/>
       </c>
       <c r="C9" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$109, $A9, 'GPT-5 Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D9" s="47">
-        <f>SUMIF('GPT-5 Generation'!$A$110:$A$116, $A9, 'GPT-5 Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A9, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E9" s="47">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$109, $A9, 'GPT-5 Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F9" s="47">

--- a/Wumple/Grading/2 stage/6-examples/Wumple_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/Wumple/Grading/2 stage/6-examples/Wumple_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Wumple" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gemini 3.1 Pro Generation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gemini 3.1 Pro Grading" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -15176,15 +15176,15 @@
         <v/>
       </c>
       <c r="C3" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A3, 'Gemini 3.1 Pro Grading'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D3" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A3, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$110:$A$116, $A3, 'Gemini 3.1 Pro Grading'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E3" s="47">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A3, 'Gemini 3.1 Pro Grading'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F3" s="47">
@@ -15212,15 +15212,15 @@
         <v/>
       </c>
       <c r="C4" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A4, 'Gemini 3.1 Pro Grading'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D4" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A4, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$110:$A$116, $A4, 'Gemini 3.1 Pro Grading'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E4" s="47">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A4, 'Gemini 3.1 Pro Grading'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F4" s="47">
@@ -15252,15 +15252,15 @@
         <v/>
       </c>
       <c r="C5" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A5, 'Gemini 3.1 Pro Grading'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D5" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A5, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$110:$A$116, $A5, 'Gemini 3.1 Pro Grading'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E5" s="47">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A5, 'Gemini 3.1 Pro Grading'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F5" s="47">
@@ -15292,15 +15292,15 @@
         <v/>
       </c>
       <c r="C6" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A6, 'Gemini 3.1 Pro Grading'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D6" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A6, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$110:$A$116, $A6, 'Gemini 3.1 Pro Grading'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E6" s="47">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A6, 'Gemini 3.1 Pro Grading'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F6" s="47">
@@ -15327,15 +15327,15 @@
         <v/>
       </c>
       <c r="C7" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A7, 'Gemini 3.1 Pro Grading'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D7" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A7, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$110:$A$116, $A7, 'Gemini 3.1 Pro Grading'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E7" s="47">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A7, 'Gemini 3.1 Pro Grading'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F7" s="47">
@@ -15367,15 +15367,15 @@
         <v/>
       </c>
       <c r="C8" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A8, 'Gemini 3.1 Pro Grading'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D8" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A8, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$110:$A$116, $A8, 'Gemini 3.1 Pro Grading'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E8" s="47">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A8, 'Gemini 3.1 Pro Grading'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F8" s="47">
@@ -15407,15 +15407,15 @@
         <v/>
       </c>
       <c r="C9" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$109)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A9, 'Gemini 3.1 Pro Grading'!$C$2:$C$109)</f>
         <v/>
       </c>
       <c r="D9" s="47">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$110:$A$116, $A9, 'Gemini 3.1 Pro Generation'!$C$110:$C$116)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$110:$A$116, $A9, 'Gemini 3.1 Pro Grading'!$C$110:$C$116)</f>
         <v/>
       </c>
       <c r="E9" s="47">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$109, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$109,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$109, $A9, 'Gemini 3.1 Pro Grading'!$C$2:$C$109,0)</f>
         <v/>
       </c>
       <c r="F9" s="47">
